--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sultan/Jobs/Camarones/Jenner/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15A08A04-5A90-5E47-A6DF-5CC27A4AA845}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1E46CDC-163D-D445-AF47-43840DB22762}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-51200" yWindow="7620" windowWidth="51200" windowHeight="28300" tabRatio="625" activeTab="2" xr2:uid="{FBD9E2A2-EFE7-4A77-BB31-BF1FB3A52DF0}"/>
+    <workbookView minimized="1" xWindow="1320" yWindow="22680" windowWidth="21220" windowHeight="23860" tabRatio="625" activeTab="1" xr2:uid="{FBD9E2A2-EFE7-4A77-BB31-BF1FB3A52DF0}"/>
   </bookViews>
   <sheets>
     <sheet name="Indices" sheetId="16" r:id="rId1"/>
@@ -1036,25 +1036,25 @@
     <xf numFmtId="0" fontId="7" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1511,7 +1511,7 @@
       <c r="I1" s="77"/>
       <c r="J1" s="77"/>
       <c r="K1" s="78"/>
-      <c r="L1" s="89" t="s">
+      <c r="L1" s="83" t="s">
         <v>1</v>
       </c>
       <c r="M1" s="79"/>
@@ -18416,6 +18416,7 @@
   <dimension ref="A1:AE242"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
+    <col min="11" max="11" width="18.33203125" customWidth="1"/>
     <col min="12" max="12" width="21.1640625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="16.33203125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="14.83203125" bestFit="1" customWidth="1"/>
@@ -18438,19 +18439,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:31" ht="16" x14ac:dyDescent="0.2">
-      <c r="A1" s="83" t="s">
+      <c r="A1" s="84" t="s">
         <v>52</v>
       </c>
-      <c r="B1" s="84"/>
-      <c r="C1" s="84"/>
-      <c r="D1" s="84"/>
-      <c r="E1" s="84"/>
-      <c r="F1" s="84"/>
-      <c r="G1" s="84"/>
-      <c r="H1" s="84"/>
-      <c r="I1" s="84"/>
-      <c r="J1" s="84"/>
-      <c r="K1" s="88"/>
+      <c r="B1" s="85"/>
+      <c r="C1" s="85"/>
+      <c r="D1" s="85"/>
+      <c r="E1" s="85"/>
+      <c r="F1" s="85"/>
+      <c r="G1" s="85"/>
+      <c r="H1" s="85"/>
+      <c r="I1" s="85"/>
+      <c r="J1" s="85"/>
+      <c r="K1" s="86"/>
       <c r="L1" s="80" t="s">
         <v>0</v>
       </c>
@@ -18465,16 +18466,16 @@
       <c r="U1" s="87" t="s">
         <v>1</v>
       </c>
-      <c r="V1" s="85"/>
-      <c r="W1" s="85"/>
-      <c r="X1" s="85"/>
-      <c r="Y1" s="85"/>
-      <c r="Z1" s="85"/>
-      <c r="AA1" s="85"/>
-      <c r="AB1" s="85"/>
-      <c r="AC1" s="85"/>
-      <c r="AD1" s="85"/>
-      <c r="AE1" s="86"/>
+      <c r="V1" s="88"/>
+      <c r="W1" s="88"/>
+      <c r="X1" s="88"/>
+      <c r="Y1" s="88"/>
+      <c r="Z1" s="88"/>
+      <c r="AA1" s="88"/>
+      <c r="AB1" s="88"/>
+      <c r="AC1" s="88"/>
+      <c r="AD1" s="88"/>
+      <c r="AE1" s="89"/>
     </row>
     <row r="2" spans="1:31" ht="18" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
